--- a/Team-Data/2013-14/4-9-2013-14.xlsx
+++ b/Team-Data/2013-14/4-9-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F2" t="n">
         <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>0.449</v>
+        <v>0.442</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J2" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L2" t="n">
         <v>9.5</v>
@@ -691,7 +758,7 @@
         <v>25.9</v>
       </c>
       <c r="N2" t="n">
-        <v>0.367</v>
+        <v>0.366</v>
       </c>
       <c r="O2" t="n">
         <v>16.9</v>
@@ -700,10 +767,10 @@
         <v>21.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.778</v>
+        <v>0.779</v>
       </c>
       <c r="R2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="S2" t="n">
         <v>31.2</v>
@@ -718,13 +785,13 @@
         <v>15.4</v>
       </c>
       <c r="W2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X2" t="n">
         <v>4</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z2" t="n">
         <v>19.2</v>
@@ -736,10 +803,10 @@
         <v>101.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -760,7 +827,7 @@
         <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
@@ -784,7 +851,7 @@
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW2" t="n">
         <v>9</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E3" t="n">
         <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G3" t="n">
-        <v>0.295</v>
+        <v>0.299</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
@@ -867,34 +934,34 @@
         <v>0.433</v>
       </c>
       <c r="L3" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.33</v>
+        <v>0.328</v>
       </c>
       <c r="O3" t="n">
         <v>16.2</v>
       </c>
       <c r="P3" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.776</v>
+        <v>0.775</v>
       </c>
       <c r="R3" t="n">
         <v>12.1</v>
       </c>
       <c r="S3" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T3" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U3" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V3" t="n">
         <v>15.3</v>
@@ -912,7 +979,7 @@
         <v>21.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AB3" t="n">
         <v>95.7</v>
@@ -921,13 +988,13 @@
         <v>-4.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
         <v>27</v>
       </c>
       <c r="AF3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="n">
         <v>27</v>
@@ -948,7 +1015,7 @@
         <v>21</v>
       </c>
       <c r="AM3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN3" t="n">
         <v>28</v>
@@ -957,13 +1024,13 @@
         <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS3" t="n">
         <v>24</v>
@@ -981,7 +1048,7 @@
         <v>23</v>
       </c>
       <c r="AX3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E4" t="n">
         <v>43</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>0.551</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1061,7 +1128,7 @@
         <v>18.4</v>
       </c>
       <c r="P4" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="Q4" t="n">
         <v>0.757</v>
@@ -1082,7 +1149,7 @@
         <v>14.3</v>
       </c>
       <c r="W4" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X4" t="n">
         <v>3.9</v>
@@ -1097,13 +1164,13 @@
         <v>20.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>98.90000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
         <v>14</v>
@@ -1133,13 +1200,13 @@
         <v>10</v>
       </c>
       <c r="AN4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO4" t="n">
         <v>11</v>
       </c>
-      <c r="AO4" t="n">
-        <v>10</v>
-      </c>
       <c r="AP4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
         <v>16</v>
@@ -1163,7 +1230,7 @@
         <v>6</v>
       </c>
       <c r="AX4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY4" t="n">
         <v>8</v>
@@ -1172,7 +1239,7 @@
         <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>20</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F5" t="n">
         <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>0.513</v>
+        <v>0.506</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
@@ -1225,37 +1292,37 @@
         <v>36.2</v>
       </c>
       <c r="J5" t="n">
-        <v>82.09999999999999</v>
+        <v>82</v>
       </c>
       <c r="K5" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L5" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M5" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.354</v>
+        <v>0.352</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P5" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.742</v>
+        <v>0.741</v>
       </c>
       <c r="R5" t="n">
         <v>9.4</v>
       </c>
       <c r="S5" t="n">
-        <v>33.2</v>
+        <v>33.1</v>
       </c>
       <c r="T5" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U5" t="n">
         <v>21.4</v>
@@ -1267,10 +1334,10 @@
         <v>6.1</v>
       </c>
       <c r="X5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Y5" t="n">
         <v>5.1</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>5.2</v>
       </c>
       <c r="Z5" t="n">
         <v>18.2</v>
@@ -1285,25 +1352,25 @@
         <v>-0.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AI5" t="n">
         <v>25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
         <v>25</v>
@@ -1315,13 +1382,13 @@
         <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO5" t="n">
         <v>14</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ5" t="n">
         <v>24</v>
@@ -1333,7 +1400,7 @@
         <v>7</v>
       </c>
       <c r="AT5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU5" t="n">
         <v>17</v>
@@ -1348,16 +1415,16 @@
         <v>9</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
         <v>2</v>
       </c>
       <c r="BA5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC5" t="n">
         <v>16</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -1389,43 +1456,43 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E6" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.59</v>
+        <v>0.584</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="J6" t="n">
         <v>80.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="L6" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M6" t="n">
         <v>17.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.35</v>
+        <v>0.347</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P6" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q6" t="n">
         <v>0.778</v>
@@ -1434,13 +1501,13 @@
         <v>11.6</v>
       </c>
       <c r="S6" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T6" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="U6" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V6" t="n">
         <v>15.1</v>
@@ -1461,13 +1528,13 @@
         <v>20.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
         <v>11</v>
@@ -1491,13 +1558,13 @@
         <v>30</v>
       </c>
       <c r="AL6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM6" t="n">
         <v>28</v>
       </c>
       <c r="AN6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO6" t="n">
         <v>13</v>
@@ -1506,7 +1573,7 @@
         <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
         <v>10</v>
@@ -1515,7 +1582,7 @@
         <v>9</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
         <v>11</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -1571,46 +1638,46 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" t="n">
         <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>0.405</v>
+        <v>0.397</v>
       </c>
       <c r="H7" t="n">
         <v>48.6</v>
       </c>
       <c r="I7" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="J7" t="n">
-        <v>84.7</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.435</v>
+        <v>0.433</v>
       </c>
       <c r="L7" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M7" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O7" t="n">
-        <v>16.9</v>
+        <v>17.1</v>
       </c>
       <c r="P7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.751</v>
+        <v>0.752</v>
       </c>
       <c r="R7" t="n">
         <v>12</v>
@@ -1622,7 +1689,7 @@
         <v>44</v>
       </c>
       <c r="U7" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="V7" t="n">
         <v>14.3</v>
@@ -1634,25 +1701,25 @@
         <v>3.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z7" t="n">
         <v>19.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>97.8</v>
+        <v>97.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3.6</v>
+        <v>-3.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF7" t="n">
         <v>22</v>
@@ -1670,7 +1737,7 @@
         <v>8</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
         <v>18</v>
@@ -1682,13 +1749,13 @@
         <v>16</v>
       </c>
       <c r="AO7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR7" t="n">
         <v>7</v>
@@ -1700,13 +1767,13 @@
         <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AV7" t="n">
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX7" t="n">
         <v>29</v>
@@ -1718,7 +1785,7 @@
         <v>9</v>
       </c>
       <c r="BA7" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BB7" t="n">
         <v>22</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1916,7 @@
         <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
         <v>5</v>
@@ -1864,7 +1931,7 @@
         <v>2</v>
       </c>
       <c r="AO8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP8" t="n">
         <v>23</v>
@@ -1876,7 +1943,7 @@
         <v>22</v>
       </c>
       <c r="AS8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT8" t="n">
         <v>26</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -1935,34 +2002,34 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F9" t="n">
         <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>0.436</v>
+        <v>0.429</v>
       </c>
       <c r="H9" t="n">
         <v>48.2</v>
       </c>
       <c r="I9" t="n">
-        <v>38.5</v>
+        <v>38.3</v>
       </c>
       <c r="J9" t="n">
-        <v>85.7</v>
+        <v>85.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L9" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="M9" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="N9" t="n">
         <v>0.363</v>
@@ -1971,31 +2038,31 @@
         <v>18.9</v>
       </c>
       <c r="P9" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.721</v>
+        <v>0.72</v>
       </c>
       <c r="R9" t="n">
         <v>12.2</v>
       </c>
       <c r="S9" t="n">
-        <v>33.1</v>
+        <v>33</v>
       </c>
       <c r="T9" t="n">
         <v>45.2</v>
       </c>
       <c r="U9" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V9" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W9" t="n">
         <v>7.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y9" t="n">
         <v>5.7</v>
@@ -2007,13 +2074,13 @@
         <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>104.4</v>
+        <v>104.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.2</v>
+        <v>-2.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
         <v>19</v>
@@ -2025,7 +2092,7 @@
         <v>19</v>
       </c>
       <c r="AH9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
         <v>12</v>
@@ -2034,7 +2101,7 @@
         <v>5</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -2117,52 +2184,52 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E10" t="n">
         <v>29</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>0.367</v>
+        <v>0.372</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J10" t="n">
-        <v>87</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L10" t="n">
         <v>6.2</v>
       </c>
       <c r="M10" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N10" t="n">
         <v>0.321</v>
       </c>
       <c r="O10" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="P10" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q10" t="n">
         <v>0.672</v>
       </c>
       <c r="R10" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T10" t="n">
         <v>45.3</v>
@@ -2174,7 +2241,7 @@
         <v>14.6</v>
       </c>
       <c r="W10" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X10" t="n">
         <v>4.9</v>
@@ -2183,7 +2250,7 @@
         <v>4.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA10" t="n">
         <v>20.5</v>
@@ -2192,10 +2259,10 @@
         <v>100.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.6</v>
+        <v>-3.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2213,22 +2280,22 @@
         <v>8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN10" t="n">
         <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP10" t="n">
         <v>6</v>
@@ -2246,7 +2313,7 @@
         <v>3</v>
       </c>
       <c r="AU10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AV10" t="n">
         <v>12</v>
@@ -2267,7 +2334,7 @@
         <v>14</v>
       </c>
       <c r="BB10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2419,7 +2486,7 @@
         <v>19</v>
       </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2434,7 +2501,7 @@
         <v>22</v>
       </c>
       <c r="AW11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX11" t="n">
         <v>10</v>
@@ -2452,7 +2519,7 @@
         <v>10</v>
       </c>
       <c r="BC11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" t="n">
         <v>52</v>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
-        <v>0.667</v>
+        <v>0.675</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
@@ -2499,28 +2566,28 @@
         <v>38.1</v>
       </c>
       <c r="J12" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0.474</v>
       </c>
       <c r="L12" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M12" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O12" t="n">
         <v>22</v>
       </c>
       <c r="P12" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.709</v>
+        <v>0.707</v>
       </c>
       <c r="R12" t="n">
         <v>11.2</v>
@@ -2529,10 +2596,10 @@
         <v>34.1</v>
       </c>
       <c r="T12" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="U12" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V12" t="n">
         <v>16.3</v>
@@ -2553,19 +2620,19 @@
         <v>24.4</v>
       </c>
       <c r="AB12" t="n">
-        <v>107.7</v>
+        <v>107.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
       </c>
       <c r="AF12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG12" t="n">
         <v>6</v>
@@ -2583,7 +2650,7 @@
         <v>4</v>
       </c>
       <c r="AL12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM12" t="n">
         <v>1</v>
@@ -2622,10 +2689,10 @@
         <v>3</v>
       </c>
       <c r="AY12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2634,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E13" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F13" t="n">
         <v>25</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
@@ -2681,7 +2748,7 @@
         <v>35.9</v>
       </c>
       <c r="J13" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K13" t="n">
         <v>0.447</v>
@@ -2690,19 +2757,19 @@
         <v>6.6</v>
       </c>
       <c r="M13" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.352</v>
+        <v>0.35</v>
       </c>
       <c r="O13" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="P13" t="n">
         <v>23.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.779</v>
+        <v>0.781</v>
       </c>
       <c r="R13" t="n">
         <v>10.2</v>
@@ -2714,10 +2781,10 @@
         <v>44.8</v>
       </c>
       <c r="U13" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V13" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W13" t="n">
         <v>6.8</v>
@@ -2735,22 +2802,22 @@
         <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="AC13" t="n">
         <v>4.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>4</v>
       </c>
       <c r="AF13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH13" t="n">
         <v>22</v>
@@ -2762,7 +2829,7 @@
         <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL13" t="n">
         <v>24</v>
@@ -2771,10 +2838,10 @@
         <v>25</v>
       </c>
       <c r="AN13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP13" t="n">
         <v>13</v>
@@ -2807,13 +2874,13 @@
         <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC13" t="n">
         <v>7</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E14" t="n">
         <v>55</v>
       </c>
       <c r="F14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>0.696</v>
+        <v>0.705</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
@@ -2866,7 +2933,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.474</v>
+        <v>0.475</v>
       </c>
       <c r="L14" t="n">
         <v>8.4</v>
@@ -2875,7 +2942,7 @@
         <v>23.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O14" t="n">
         <v>21.1</v>
@@ -2884,16 +2951,16 @@
         <v>28.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="R14" t="n">
         <v>10.5</v>
       </c>
       <c r="S14" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T14" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U14" t="n">
         <v>24.5</v>
@@ -2902,13 +2969,13 @@
         <v>13.9</v>
       </c>
       <c r="W14" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X14" t="n">
         <v>4.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z14" t="n">
         <v>21.5</v>
@@ -2917,13 +2984,13 @@
         <v>23.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.7</v>
+        <v>107.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2935,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
@@ -2971,7 +3038,7 @@
         <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU14" t="n">
         <v>3</v>
@@ -2986,13 +3053,13 @@
         <v>13</v>
       </c>
       <c r="AY14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ14" t="n">
         <v>20</v>
       </c>
       <c r="BA14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3126,7 +3193,7 @@
         <v>6</v>
       </c>
       <c r="AK15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL15" t="n">
         <v>4</v>
@@ -3141,7 +3208,7 @@
         <v>16</v>
       </c>
       <c r="AP15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ15" t="n">
         <v>18</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -3209,37 +3276,37 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F16" t="n">
         <v>32</v>
       </c>
       <c r="G16" t="n">
-        <v>0.59</v>
+        <v>0.584</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J16" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K16" t="n">
-        <v>0.462</v>
+        <v>0.461</v>
       </c>
       <c r="L16" t="n">
         <v>4.9</v>
       </c>
       <c r="M16" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="N16" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O16" t="n">
         <v>15.1</v>
@@ -3248,7 +3315,7 @@
         <v>20.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.743</v>
+        <v>0.744</v>
       </c>
       <c r="R16" t="n">
         <v>11.5</v>
@@ -3260,7 +3327,7 @@
         <v>42.1</v>
       </c>
       <c r="U16" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V16" t="n">
         <v>13.5</v>
@@ -3272,22 +3339,22 @@
         <v>4.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z16" t="n">
         <v>19.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.7</v>
+        <v>95.5</v>
       </c>
       <c r="AC16" t="n">
         <v>1.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3302,7 +3369,7 @@
         <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ16" t="n">
         <v>23</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -3329,10 +3396,10 @@
         <v>23</v>
       </c>
       <c r="AR16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
         <v>21</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17" t="n">
         <v>53</v>
       </c>
       <c r="F17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>0.679</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
@@ -3415,31 +3482,31 @@
         <v>0.503</v>
       </c>
       <c r="L17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M17" t="n">
         <v>22.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.367</v>
+        <v>0.364</v>
       </c>
       <c r="O17" t="n">
         <v>17.6</v>
       </c>
       <c r="P17" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R17" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="S17" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="U17" t="n">
         <v>22.8</v>
@@ -3451,13 +3518,13 @@
         <v>8.9</v>
       </c>
       <c r="X17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y17" t="n">
         <v>3.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA17" t="n">
         <v>20.4</v>
@@ -3466,25 +3533,25 @@
         <v>102.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF17" t="n">
         <v>4</v>
       </c>
       <c r="AG17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH17" t="n">
         <v>6</v>
       </c>
       <c r="AI17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3499,7 +3566,7 @@
         <v>15</v>
       </c>
       <c r="AN17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO17" t="n">
         <v>15</v>
@@ -3508,13 +3575,13 @@
         <v>17</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -3573,43 +3640,43 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E18" t="n">
         <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G18" t="n">
-        <v>0.179</v>
+        <v>0.182</v>
       </c>
       <c r="H18" t="n">
         <v>48.5</v>
       </c>
       <c r="I18" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J18" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K18" t="n">
         <v>0.435</v>
       </c>
       <c r="L18" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M18" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O18" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P18" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q18" t="n">
         <v>0.752</v>
@@ -3618,10 +3685,10 @@
         <v>11.9</v>
       </c>
       <c r="S18" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T18" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U18" t="n">
         <v>21.5</v>
@@ -3645,13 +3712,13 @@
         <v>20.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="AC18" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3672,31 +3739,31 @@
         <v>17</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL18" t="n">
         <v>22</v>
       </c>
       <c r="AM18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP18" t="n">
         <v>20</v>
       </c>
       <c r="AQ18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR18" t="n">
         <v>8</v>
       </c>
       <c r="AS18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT18" t="n">
         <v>23</v>
@@ -3714,7 +3781,7 @@
         <v>11</v>
       </c>
       <c r="AY18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ18" t="n">
         <v>18</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -3755,25 +3822,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E19" t="n">
         <v>39</v>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.506</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J19" t="n">
-        <v>87.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="K19" t="n">
         <v>0.445</v>
@@ -3785,16 +3852,16 @@
         <v>21.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="O19" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="P19" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R19" t="n">
         <v>12.5</v>
@@ -3803,58 +3870,58 @@
         <v>32.3</v>
       </c>
       <c r="T19" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="U19" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="V19" t="n">
         <v>13.9</v>
       </c>
       <c r="W19" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X19" t="n">
         <v>3.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z19" t="n">
         <v>18.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.4</v>
+        <v>106.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH19" t="n">
         <v>17</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>18</v>
       </c>
       <c r="AI19" t="n">
         <v>7</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL19" t="n">
         <v>17</v>
@@ -3872,13 +3939,13 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT19" t="n">
         <v>8</v>
@@ -3896,19 +3963,19 @@
         <v>30</v>
       </c>
       <c r="AY19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ19" t="n">
         <v>3</v>
       </c>
       <c r="BA19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB19" t="n">
         <v>3</v>
       </c>
-      <c r="BB19" t="n">
-        <v>4</v>
-      </c>
       <c r="BC19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -3937,22 +4004,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E20" t="n">
         <v>32</v>
       </c>
       <c r="F20" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G20" t="n">
-        <v>0.41</v>
+        <v>0.416</v>
       </c>
       <c r="H20" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="J20" t="n">
         <v>82.40000000000001</v>
@@ -3967,13 +4034,13 @@
         <v>15.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O20" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P20" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="Q20" t="n">
         <v>0.77</v>
@@ -3982,13 +4049,13 @@
         <v>11.5</v>
       </c>
       <c r="S20" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T20" t="n">
         <v>41.8</v>
       </c>
       <c r="U20" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V20" t="n">
         <v>13.9</v>
@@ -4006,34 +4073,34 @@
         <v>22.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.7</v>
+        <v>-2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
         <v>21</v>
       </c>
       <c r="AF20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG20" t="n">
         <v>21</v>
       </c>
       <c r="AH20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AK20" t="n">
         <v>11</v>
@@ -4045,7 +4112,7 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
         <v>12</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>-1.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF21" t="n">
         <v>20</v>
@@ -4209,16 +4276,16 @@
         <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ21" t="n">
         <v>16</v>
       </c>
       <c r="AK21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL21" t="n">
         <v>6</v>
@@ -4230,7 +4297,7 @@
         <v>7</v>
       </c>
       <c r="AO21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AP21" t="n">
         <v>30</v>
@@ -4254,19 +4321,19 @@
         <v>2</v>
       </c>
       <c r="AW21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX21" t="n">
         <v>19</v>
       </c>
       <c r="AY21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ21" t="n">
         <v>23</v>
       </c>
       <c r="BA21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -4301,43 +4368,43 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E22" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F22" t="n">
         <v>21</v>
       </c>
       <c r="G22" t="n">
-        <v>0.731</v>
+        <v>0.727</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J22" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O22" t="n">
         <v>20</v>
       </c>
       <c r="P22" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q22" t="n">
         <v>0.804</v>
@@ -4352,10 +4419,10 @@
         <v>44.8</v>
       </c>
       <c r="U22" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V22" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W22" t="n">
         <v>8.199999999999999</v>
@@ -4379,7 +4446,7 @@
         <v>6.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
         <v>5</v>
@@ -4409,7 +4476,7 @@
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4424,7 +4491,7 @@
         <v>20</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
         <v>6</v>
@@ -4433,7 +4500,7 @@
         <v>14</v>
       </c>
       <c r="AV22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -4483,46 +4550,46 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F23" t="n">
         <v>55</v>
       </c>
       <c r="G23" t="n">
-        <v>0.295</v>
+        <v>0.286</v>
       </c>
       <c r="H23" t="n">
         <v>48.7</v>
       </c>
       <c r="I23" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J23" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L23" t="n">
         <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O23" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="P23" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.763</v>
+        <v>0.766</v>
       </c>
       <c r="R23" t="n">
         <v>9.800000000000001</v>
@@ -4531,10 +4598,10 @@
         <v>32.6</v>
       </c>
       <c r="T23" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U23" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V23" t="n">
         <v>14.8</v>
@@ -4543,46 +4610,46 @@
         <v>7.6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA23" t="n">
         <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.1</v>
+        <v>-5.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH23" t="n">
         <v>2</v>
       </c>
       <c r="AI23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
         <v>13</v>
       </c>
       <c r="AK23" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL23" t="n">
         <v>20</v>
@@ -4591,13 +4658,13 @@
         <v>21</v>
       </c>
       <c r="AN23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO23" t="n">
         <v>26</v>
       </c>
       <c r="AP23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AQ23" t="n">
         <v>12</v>
@@ -4612,19 +4679,19 @@
         <v>19</v>
       </c>
       <c r="AU23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV23" t="n">
         <v>17</v>
       </c>
       <c r="AW23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX23" t="n">
         <v>22</v>
       </c>
       <c r="AY23" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AZ23" t="n">
         <v>13</v>
@@ -4633,7 +4700,7 @@
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E24" t="n">
         <v>17</v>
       </c>
       <c r="F24" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G24" t="n">
-        <v>0.218</v>
+        <v>0.221</v>
       </c>
       <c r="H24" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I24" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J24" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.432</v>
+        <v>0.431</v>
       </c>
       <c r="L24" t="n">
         <v>7.1</v>
@@ -4695,25 +4762,25 @@
         <v>22.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.313</v>
+        <v>0.312</v>
       </c>
       <c r="O24" t="n">
         <v>16.6</v>
       </c>
       <c r="P24" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.711</v>
+        <v>0.709</v>
       </c>
       <c r="R24" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S24" t="n">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="T24" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U24" t="n">
         <v>21.9</v>
@@ -4722,7 +4789,7 @@
         <v>17</v>
       </c>
       <c r="W24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X24" t="n">
         <v>4</v>
@@ -4731,19 +4798,19 @@
         <v>6.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>99.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC24" t="n">
         <v>-10.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,13 +4822,13 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI24" t="n">
         <v>17</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK24" t="n">
         <v>29</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP24" t="n">
         <v>15</v>
@@ -4788,10 +4855,10 @@
         <v>9</v>
       </c>
       <c r="AS24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU24" t="n">
         <v>13</v>
@@ -4812,7 +4879,7 @@
         <v>25</v>
       </c>
       <c r="BA24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB24" t="n">
         <v>19</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F25" t="n">
         <v>31</v>
       </c>
       <c r="G25" t="n">
-        <v>0.603</v>
+        <v>0.597</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4874,34 +4941,34 @@
         <v>9.4</v>
       </c>
       <c r="M25" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.374</v>
+        <v>0.373</v>
       </c>
       <c r="O25" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="P25" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q25" t="n">
         <v>0.758</v>
       </c>
       <c r="R25" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S25" t="n">
         <v>31.8</v>
       </c>
       <c r="T25" t="n">
-        <v>43.2</v>
+        <v>43.3</v>
       </c>
       <c r="U25" t="n">
         <v>19.2</v>
       </c>
       <c r="V25" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W25" t="n">
         <v>8.300000000000001</v>
@@ -4916,16 +4983,16 @@
         <v>22.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.5</v>
+        <v>105.7</v>
       </c>
       <c r="AC25" t="n">
         <v>2.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
@@ -4943,13 +5010,13 @@
         <v>9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK25" t="n">
         <v>7</v>
       </c>
       <c r="AL25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM25" t="n">
         <v>4</v>
@@ -4961,13 +5028,13 @@
         <v>9</v>
       </c>
       <c r="AP25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ25" t="n">
         <v>15</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS25" t="n">
         <v>16</v>
@@ -4979,7 +5046,7 @@
         <v>29</v>
       </c>
       <c r="AV25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E26" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F26" t="n">
         <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.646</v>
+        <v>0.641</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5047,7 +5114,7 @@
         <v>39</v>
       </c>
       <c r="J26" t="n">
-        <v>86.8</v>
+        <v>87</v>
       </c>
       <c r="K26" t="n">
         <v>0.449</v>
@@ -5068,10 +5135,10 @@
         <v>23.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S26" t="n">
         <v>33.8</v>
@@ -5092,7 +5159,7 @@
         <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z26" t="n">
         <v>19.4</v>
@@ -5101,13 +5168,13 @@
         <v>20.7</v>
       </c>
       <c r="AB26" t="n">
-        <v>106.5</v>
+        <v>106.6</v>
       </c>
       <c r="AC26" t="n">
         <v>3.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
@@ -5125,10 +5192,10 @@
         <v>6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
@@ -5137,7 +5204,7 @@
         <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO26" t="n">
         <v>7</v>
@@ -5149,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS26" t="n">
         <v>6</v>
@@ -5179,7 +5246,7 @@
         <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC26" t="n">
         <v>8</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -5211,37 +5278,37 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E27" t="n">
         <v>27</v>
       </c>
       <c r="F27" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G27" t="n">
-        <v>0.342</v>
+        <v>0.346</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J27" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>0.447</v>
       </c>
       <c r="L27" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M27" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.334</v>
+        <v>0.333</v>
       </c>
       <c r="O27" t="n">
         <v>20.7</v>
@@ -5277,19 +5344,19 @@
         <v>5.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="AA27" t="n">
         <v>23.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>100.4</v>
+        <v>100.5</v>
       </c>
       <c r="AC27" t="n">
         <v>-2.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5307,7 +5374,7 @@
         <v>21</v>
       </c>
       <c r="AJ27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK27" t="n">
         <v>19</v>
@@ -5328,16 +5395,16 @@
         <v>4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5349,7 +5416,7 @@
         <v>22</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY27" t="n">
         <v>25</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>8.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5483,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="AH28" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5540,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB28" t="n">
         <v>7</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E29" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F29" t="n">
         <v>32</v>
       </c>
       <c r="G29" t="n">
-        <v>0.59</v>
+        <v>0.584</v>
       </c>
       <c r="H29" t="n">
         <v>48.7</v>
@@ -5596,7 +5663,7 @@
         <v>82.09999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L29" t="n">
         <v>8.5</v>
@@ -5605,34 +5672,34 @@
         <v>23.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.37</v>
+        <v>0.368</v>
       </c>
       <c r="O29" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="P29" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="R29" t="n">
         <v>11.4</v>
       </c>
       <c r="S29" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="T29" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U29" t="n">
         <v>21.2</v>
       </c>
       <c r="V29" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W29" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X29" t="n">
         <v>4.2</v>
@@ -5641,19 +5708,19 @@
         <v>4.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA29" t="n">
         <v>22</v>
       </c>
       <c r="AB29" t="n">
-        <v>101.1</v>
+        <v>100.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
@@ -5671,7 +5738,7 @@
         <v>23</v>
       </c>
       <c r="AJ29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="n">
         <v>22</v>
@@ -5683,13 +5750,13 @@
         <v>11</v>
       </c>
       <c r="AN29" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO29" t="n">
         <v>6</v>
       </c>
       <c r="AP29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ29" t="n">
         <v>5</v>
@@ -5701,7 +5768,7 @@
         <v>20</v>
       </c>
       <c r="AT29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU29" t="n">
         <v>20</v>
@@ -5710,10 +5777,10 @@
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5725,10 +5792,10 @@
         <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-7.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
         <v>26</v>
@@ -5847,7 +5914,7 @@
         <v>26</v>
       </c>
       <c r="AH30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI30" t="n">
         <v>29</v>
@@ -5877,7 +5944,7 @@
         <v>22</v>
       </c>
       <c r="AR30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS30" t="n">
         <v>26</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
@@ -5939,22 +6006,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E31" t="n">
         <v>40</v>
       </c>
       <c r="F31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G31" t="n">
-        <v>0.513</v>
+        <v>0.519</v>
       </c>
       <c r="H31" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="I31" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J31" t="n">
         <v>84.5</v>
@@ -5963,13 +6030,13 @@
         <v>0.456</v>
       </c>
       <c r="L31" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M31" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.382</v>
+        <v>0.385</v>
       </c>
       <c r="O31" t="n">
         <v>15.3</v>
@@ -5978,13 +6045,13 @@
         <v>20.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.731</v>
+        <v>0.732</v>
       </c>
       <c r="R31" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S31" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T31" t="n">
         <v>42.3</v>
@@ -5999,25 +6066,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="X31" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA31" t="n">
         <v>19.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.3</v>
+        <v>100.4</v>
       </c>
       <c r="AC31" t="n">
         <v>0.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6038,13 +6105,13 @@
         <v>9</v>
       </c>
       <c r="AK31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL31" t="n">
         <v>16</v>
       </c>
       <c r="AM31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN31" t="n">
         <v>3</v>
@@ -6059,7 +6126,7 @@
         <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AS31" t="n">
         <v>17</v>
@@ -6086,7 +6153,7 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>17</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-9-2013-14</t>
+          <t>2014-04-09</t>
         </is>
       </c>
     </row>
